--- a/erp-server/erp-server-oms/src/main/resources/excel/deliveryBoxRuleTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/deliveryBoxRuleTemplate.xlsx
@@ -32,6 +32,13 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -47,6 +54,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -67,16 +81,22 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
         <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>发货箱规</t>
+      <t>单箱数量</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -101,7 +121,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -258,6 +278,12 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1044,7 +1070,7 @@
     <col min="4" max="4" width="7.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" spans="1:7">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
